--- a/Oyacachi-Guacamayos/test.xlsx
+++ b/Oyacachi-Guacamayos/test.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T153"/>
+  <dimension ref="A1:V153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,17 +511,27 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>Sample-ID</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>sample-ID</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>altitud</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>species (det 2008!)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>[C]%_new</t>
         </is>
       </c>
     </row>
@@ -535,8 +545,10 @@
       <c r="C2" t="n">
         <v>4039</v>
       </c>
-      <c r="D2" t="n">
-        <v>82</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -585,9 +597,15 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>p82-4039</t>
+        </is>
+      </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -599,8 +617,10 @@
       <c r="C3" t="n">
         <v>4020</v>
       </c>
-      <c r="D3" t="n">
-        <v>81</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -647,9 +667,15 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>p81-4020</t>
+        </is>
+      </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -661,8 +687,10 @@
       <c r="C4" t="n">
         <v>4021</v>
       </c>
-      <c r="D4" t="n">
-        <v>81</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -709,9 +737,15 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>p81-4021</t>
+        </is>
+      </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -723,8 +757,10 @@
       <c r="C5" t="n">
         <v>4022</v>
       </c>
-      <c r="D5" t="n">
-        <v>81</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -771,9 +807,15 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>p81-4022</t>
+        </is>
+      </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -785,8 +827,10 @@
       <c r="C6" t="n">
         <v>4027</v>
       </c>
-      <c r="D6" t="n">
-        <v>81</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -833,9 +877,15 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>p81-4027</t>
+        </is>
+      </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -847,8 +897,10 @@
       <c r="C7" t="n">
         <v>4034</v>
       </c>
-      <c r="D7" t="n">
-        <v>82</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -895,9 +947,15 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>p82-4034</t>
+        </is>
+      </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -909,8 +967,10 @@
       <c r="C8" t="n">
         <v>4035</v>
       </c>
-      <c r="D8" t="n">
-        <v>82</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -957,9 +1017,15 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>p82-4035</t>
+        </is>
+      </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -971,8 +1037,10 @@
       <c r="C9" t="n">
         <v>4038</v>
       </c>
-      <c r="D9" t="n">
-        <v>82</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1019,9 +1087,15 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>p82-4038</t>
+        </is>
+      </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1033,8 +1107,10 @@
       <c r="C10" t="n">
         <v>4043</v>
       </c>
-      <c r="D10" t="n">
-        <v>82</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1077,9 +1153,15 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>p82-4043</t>
+        </is>
+      </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1091,8 +1173,10 @@
       <c r="C11" t="n">
         <v>4044</v>
       </c>
-      <c r="D11" t="n">
-        <v>82</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1139,9 +1223,15 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>p82-4044</t>
+        </is>
+      </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1153,8 +1243,10 @@
       <c r="C12" t="n">
         <v>4045</v>
       </c>
-      <c r="D12" t="n">
-        <v>82</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1201,9 +1293,15 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>p82-4045</t>
+        </is>
+      </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1215,8 +1313,10 @@
       <c r="C13" t="n">
         <v>4046</v>
       </c>
-      <c r="D13" t="n">
-        <v>82</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1238,10 +1338,10 @@
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>45.19504301335867</v>
+        <v>0.4549</v>
       </c>
       <c r="K13" t="n">
-        <v>-24.09</v>
+        <v>-27.6</v>
       </c>
       <c r="L13" t="n">
         <v>1.64177197757741</v>
@@ -1263,9 +1363,17 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>p82-4046</t>
+        </is>
+      </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.4549</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1277,8 +1385,10 @@
       <c r="C14" t="n">
         <v>4050</v>
       </c>
-      <c r="D14" t="n">
-        <v>82</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1325,9 +1435,15 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>p82-4050</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1339,8 +1455,10 @@
       <c r="C15" t="n">
         <v>4100</v>
       </c>
-      <c r="D15" t="n">
-        <v>85</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1387,9 +1505,15 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>p85-4100</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1401,8 +1525,10 @@
       <c r="C16" t="n">
         <v>4101</v>
       </c>
-      <c r="D16" t="n">
-        <v>85</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1449,9 +1575,15 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>p85-4101</t>
+        </is>
+      </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1463,8 +1595,10 @@
       <c r="C17" t="n">
         <v>4105</v>
       </c>
-      <c r="D17" t="n">
-        <v>85</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1511,9 +1645,15 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>p85-4105</t>
+        </is>
+      </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1525,8 +1665,10 @@
       <c r="C18" t="n">
         <v>4106</v>
       </c>
-      <c r="D18" t="n">
-        <v>85</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1573,9 +1715,15 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>p85-4106</t>
+        </is>
+      </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1587,8 +1735,10 @@
       <c r="C19" t="n">
         <v>4110</v>
       </c>
-      <c r="D19" t="n">
-        <v>85</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1635,9 +1785,15 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>p85-4110</t>
+        </is>
+      </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1649,8 +1805,10 @@
       <c r="C20" t="n">
         <v>4115</v>
       </c>
-      <c r="D20" t="n">
-        <v>85</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1697,9 +1855,15 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>p85-4115</t>
+        </is>
+      </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1711,8 +1875,10 @@
       <c r="C21" t="n">
         <v>4240</v>
       </c>
-      <c r="D21" t="n">
-        <v>83</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1759,9 +1925,15 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>p83-4240</t>
+        </is>
+      </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1773,8 +1945,10 @@
       <c r="C22" t="n">
         <v>4241</v>
       </c>
-      <c r="D22" t="n">
-        <v>83</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1821,9 +1995,15 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>p83-4241</t>
+        </is>
+      </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1835,8 +2015,10 @@
       <c r="C23" t="n">
         <v>4242</v>
       </c>
-      <c r="D23" t="n">
-        <v>83</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1883,9 +2065,15 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>p83-4242</t>
+        </is>
+      </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -1897,8 +2085,10 @@
       <c r="C24" t="n">
         <v>4244</v>
       </c>
-      <c r="D24" t="n">
-        <v>83</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1945,9 +2135,15 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>p83-4244</t>
+        </is>
+      </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -1959,8 +2155,10 @@
       <c r="C25" t="n">
         <v>4248</v>
       </c>
-      <c r="D25" t="n">
-        <v>83</v>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -2007,9 +2205,15 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>p83-4248</t>
+        </is>
+      </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -2021,8 +2225,10 @@
       <c r="C26" t="n">
         <v>4249</v>
       </c>
-      <c r="D26" t="n">
-        <v>83</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -2065,9 +2271,15 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>p83-4249</t>
+        </is>
+      </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -2079,8 +2291,10 @@
       <c r="C27" t="n">
         <v>4250</v>
       </c>
-      <c r="D27" t="n">
-        <v>83</v>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2127,13 +2341,19 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>p83-4250</t>
+        </is>
+      </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="B28" t="n">
         <v>8186</v>
@@ -2141,8 +2361,10 @@
       <c r="C28" t="n">
         <v>157</v>
       </c>
-      <c r="D28" t="n">
-        <v>6</v>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2184,18 +2406,24 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R28" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>p06-8186</t>
+        </is>
+      </c>
+      <c r="S28" t="n">
         <v>8186</v>
       </c>
-      <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="B29" t="n">
         <v>8194</v>
@@ -2203,8 +2431,10 @@
       <c r="C29" t="n">
         <v>161</v>
       </c>
-      <c r="D29" t="n">
-        <v>6</v>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2246,18 +2476,24 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R29" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>p06-8194</t>
+        </is>
+      </c>
+      <c r="S29" t="n">
         <v>8194</v>
       </c>
-      <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="B30" t="n">
         <v>8194</v>
@@ -2265,8 +2501,10 @@
       <c r="C30" t="n">
         <v>161</v>
       </c>
-      <c r="D30" t="n">
-        <v>6</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2308,18 +2546,24 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R30" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>p06-8194</t>
+        </is>
+      </c>
+      <c r="S30" t="n">
         <v>8194</v>
       </c>
-      <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="B31" t="n">
         <v>8188</v>
@@ -2327,8 +2571,10 @@
       <c r="C31" t="n">
         <v>158</v>
       </c>
-      <c r="D31" t="n">
-        <v>6</v>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2370,18 +2616,24 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R31" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>p06-8188</t>
+        </is>
+      </c>
+      <c r="S31" t="n">
         <v>8188</v>
       </c>
-      <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="B32" t="n">
         <v>8182</v>
@@ -2389,8 +2641,10 @@
       <c r="C32" t="n">
         <v>151</v>
       </c>
-      <c r="D32" t="n">
-        <v>6</v>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2410,10 +2664,10 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>45.65</v>
+        <v>0.4385</v>
       </c>
       <c r="K32" t="n">
-        <v>-30.25</v>
+        <v>-30.05</v>
       </c>
       <c r="L32" t="n">
         <v>1.69199067733282</v>
@@ -2432,18 +2686,26 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R32" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>p06-8182</t>
+        </is>
+      </c>
+      <c r="S32" t="n">
         <v>8182</v>
       </c>
-      <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="n">
+        <v>0.4385</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="B33" t="n">
         <v>8147</v>
@@ -2451,8 +2713,10 @@
       <c r="C33" t="n">
         <v>178</v>
       </c>
-      <c r="D33" t="n">
-        <v>7</v>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2494,18 +2758,24 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R33" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>p07-8147</t>
+        </is>
+      </c>
+      <c r="S33" t="n">
         <v>8147</v>
       </c>
-      <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="B34" t="n">
         <v>8151</v>
@@ -2513,8 +2783,10 @@
       <c r="C34" t="n">
         <v>186</v>
       </c>
-      <c r="D34" t="n">
-        <v>7</v>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2534,10 +2806,10 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>46.3</v>
+        <v>0.4617</v>
       </c>
       <c r="K34" t="n">
-        <v>-26.81</v>
+        <v>-26.78</v>
       </c>
       <c r="L34" t="n">
         <v>1.5419363634401</v>
@@ -2556,18 +2828,26 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R34" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>p07-8151</t>
+        </is>
+      </c>
+      <c r="S34" t="n">
         <v>8151</v>
       </c>
-      <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="n">
+        <v>0.4617</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B35" t="n">
         <v>8136</v>
@@ -2575,8 +2855,10 @@
       <c r="C35" t="n">
         <v>218</v>
       </c>
-      <c r="D35" t="n">
-        <v>8</v>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2618,18 +2900,24 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R35" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>p08-8136</t>
+        </is>
+      </c>
+      <c r="S35" t="n">
         <v>8136</v>
       </c>
-      <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="B36" t="n">
         <v>8135</v>
@@ -2637,8 +2925,10 @@
       <c r="C36" t="n">
         <v>214</v>
       </c>
-      <c r="D36" t="n">
-        <v>8</v>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2680,18 +2970,24 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R36" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>p08-8135</t>
+        </is>
+      </c>
+      <c r="S36" t="n">
         <v>8135</v>
       </c>
-      <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="B37" t="n">
         <v>8133</v>
@@ -2699,8 +2995,10 @@
       <c r="C37" t="n">
         <v>209</v>
       </c>
-      <c r="D37" t="n">
-        <v>8</v>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2742,18 +3040,24 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R37" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>p08-8133</t>
+        </is>
+      </c>
+      <c r="S37" t="n">
         <v>8133</v>
       </c>
-      <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B38" t="n">
         <v>8120</v>
@@ -2761,8 +3065,10 @@
       <c r="C38" t="n">
         <v>1645</v>
       </c>
-      <c r="D38" t="n">
-        <v>55</v>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2804,18 +3110,24 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R38" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>p55-8120</t>
+        </is>
+      </c>
+      <c r="S38" t="n">
         <v>8120</v>
       </c>
-      <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B39" t="n">
         <v>8123</v>
@@ -2823,8 +3135,10 @@
       <c r="C39" t="n">
         <v>1648</v>
       </c>
-      <c r="D39" t="n">
-        <v>55</v>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2866,18 +3180,24 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R39" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>p55-8123</t>
+        </is>
+      </c>
+      <c r="S39" t="n">
         <v>8123</v>
       </c>
-      <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="B40" t="n">
         <v>8122</v>
@@ -2885,8 +3205,10 @@
       <c r="C40" t="n">
         <v>1649</v>
       </c>
-      <c r="D40" t="n">
-        <v>55</v>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2928,18 +3250,24 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R40" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>p55-8122</t>
+        </is>
+      </c>
+      <c r="S40" t="n">
         <v>8122</v>
       </c>
-      <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="B41" t="n">
         <v>4039</v>
@@ -2947,8 +3275,10 @@
       <c r="C41" t="n">
         <v>4039</v>
       </c>
-      <c r="D41" t="n">
-        <v>82</v>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2990,18 +3320,24 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R41" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>p82-4039</t>
+        </is>
+      </c>
+      <c r="S41" t="n">
         <v>4039</v>
       </c>
-      <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="B42" t="n">
         <v>8016</v>
@@ -3009,8 +3345,10 @@
       <c r="C42" t="n">
         <v>4020</v>
       </c>
-      <c r="D42" t="n">
-        <v>81</v>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -3052,18 +3390,24 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R42" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>p81-8016</t>
+        </is>
+      </c>
+      <c r="S42" t="n">
         <v>8016</v>
       </c>
-      <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="B43" t="n">
         <v>8013</v>
@@ -3071,8 +3415,10 @@
       <c r="C43" t="n">
         <v>4021</v>
       </c>
-      <c r="D43" t="n">
-        <v>81</v>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -3110,16 +3456,22 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr"/>
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>p81-8013</t>
+        </is>
+      </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="B44" t="n">
         <v>8039</v>
@@ -3127,8 +3479,10 @@
       <c r="C44" t="n">
         <v>4022</v>
       </c>
-      <c r="D44" t="n">
-        <v>81</v>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -3170,18 +3524,24 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R44" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>p81-8039</t>
+        </is>
+      </c>
+      <c r="S44" t="n">
         <v>8039</v>
       </c>
-      <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="B45" t="n">
         <v>8052</v>
@@ -3189,8 +3549,10 @@
       <c r="C45" t="n">
         <v>4027</v>
       </c>
-      <c r="D45" t="n">
-        <v>81</v>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -3232,18 +3594,24 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R45" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>p81-8052</t>
+        </is>
+      </c>
+      <c r="S45" t="n">
         <v>8052</v>
       </c>
-      <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="B46" t="n">
         <v>4034</v>
@@ -3251,8 +3619,10 @@
       <c r="C46" t="n">
         <v>4034</v>
       </c>
-      <c r="D46" t="n">
-        <v>82</v>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -3294,18 +3664,24 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R46" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>p82-4034</t>
+        </is>
+      </c>
+      <c r="S46" t="n">
         <v>4034</v>
       </c>
-      <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="B47" t="n">
         <v>4036</v>
@@ -3313,8 +3689,10 @@
       <c r="C47" t="n">
         <v>4035</v>
       </c>
-      <c r="D47" t="n">
-        <v>82</v>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -3356,18 +3734,24 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R47" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>p82-4036</t>
+        </is>
+      </c>
+      <c r="S47" t="n">
         <v>4036</v>
       </c>
-      <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="B48" t="n">
         <v>4038</v>
@@ -3375,8 +3759,10 @@
       <c r="C48" t="n">
         <v>4038</v>
       </c>
-      <c r="D48" t="n">
-        <v>82</v>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -3418,18 +3804,24 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R48" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>p82-4038</t>
+        </is>
+      </c>
+      <c r="S48" t="n">
         <v>4038</v>
       </c>
-      <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="B49" t="n">
         <v>8080</v>
@@ -3437,8 +3829,10 @@
       <c r="C49" t="n">
         <v>4043</v>
       </c>
-      <c r="D49" t="n">
-        <v>82</v>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -3480,18 +3874,24 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R49" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>p82-8080</t>
+        </is>
+      </c>
+      <c r="S49" t="n">
         <v>8080</v>
       </c>
-      <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="B50" t="n">
         <v>4044</v>
@@ -3499,8 +3899,10 @@
       <c r="C50" t="n">
         <v>4044</v>
       </c>
-      <c r="D50" t="n">
-        <v>82</v>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -3542,18 +3944,24 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R50" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>p82-4044</t>
+        </is>
+      </c>
+      <c r="S50" t="n">
         <v>4044</v>
       </c>
-      <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="B51" t="n">
         <v>4045</v>
@@ -3561,8 +3969,10 @@
       <c r="C51" t="n">
         <v>4045</v>
       </c>
-      <c r="D51" t="n">
-        <v>82</v>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -3604,18 +4014,24 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R51" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>p82-4045</t>
+        </is>
+      </c>
+      <c r="S51" t="n">
         <v>4045</v>
       </c>
-      <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="B52" t="n">
         <v>4046</v>
@@ -3623,8 +4039,10 @@
       <c r="C52" t="n">
         <v>4046</v>
       </c>
-      <c r="D52" t="n">
-        <v>82</v>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -3644,10 +4062,10 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="n">
-        <v>10.87497569184914</v>
+        <v>0.4549</v>
       </c>
       <c r="K52" t="n">
-        <v>-27.29</v>
+        <v>-27.6</v>
       </c>
       <c r="L52" t="n">
         <v>1.70042225244169</v>
@@ -3666,18 +4084,26 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R52" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>p82-4046</t>
+        </is>
+      </c>
+      <c r="S52" t="n">
         <v>4046</v>
       </c>
-      <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="n">
+        <v>0.4549</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="B53" t="n">
         <v>4050</v>
@@ -3685,8 +4111,10 @@
       <c r="C53" t="n">
         <v>4050</v>
       </c>
-      <c r="D53" t="n">
-        <v>82</v>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -3728,18 +4156,24 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R53" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>p82-4050</t>
+        </is>
+      </c>
+      <c r="S53" t="n">
         <v>4050</v>
       </c>
-      <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="B54" t="n">
         <v>4055</v>
@@ -3747,8 +4181,10 @@
       <c r="C54" t="n">
         <v>4055</v>
       </c>
-      <c r="D54" t="n">
-        <v>83</v>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -3790,18 +4226,24 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R54" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>p83-4055</t>
+        </is>
+      </c>
+      <c r="S54" t="n">
         <v>4055</v>
       </c>
-      <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="B55" t="n">
         <v>8066</v>
@@ -3809,8 +4251,10 @@
       <c r="C55" t="n">
         <v>4100</v>
       </c>
-      <c r="D55" t="n">
-        <v>85</v>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -3848,16 +4292,22 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr"/>
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>p85-8066</t>
+        </is>
+      </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="B56" t="n">
         <v>8067</v>
@@ -3865,8 +4315,10 @@
       <c r="C56" t="n">
         <v>4101</v>
       </c>
-      <c r="D56" t="n">
-        <v>85</v>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -3908,18 +4360,24 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R56" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>p85-8067</t>
+        </is>
+      </c>
+      <c r="S56" t="n">
         <v>8067</v>
       </c>
-      <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="B57" t="n">
         <v>8071</v>
@@ -3927,8 +4385,10 @@
       <c r="C57" t="n">
         <v>4105</v>
       </c>
-      <c r="D57" t="n">
-        <v>85</v>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -3970,18 +4430,24 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R57" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>p85-8071</t>
+        </is>
+      </c>
+      <c r="S57" t="n">
         <v>8071</v>
       </c>
-      <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="B58" t="n">
         <v>8076</v>
@@ -3989,8 +4455,10 @@
       <c r="C58" t="n">
         <v>4106</v>
       </c>
-      <c r="D58" t="n">
-        <v>85</v>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -4032,18 +4500,24 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R58" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>p85-8076</t>
+        </is>
+      </c>
+      <c r="S58" t="n">
         <v>8076</v>
       </c>
-      <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="B59" t="n">
         <v>4110</v>
@@ -4051,8 +4525,10 @@
       <c r="C59" t="n">
         <v>4110</v>
       </c>
-      <c r="D59" t="n">
-        <v>85</v>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -4090,16 +4566,22 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr"/>
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>p85-4110</t>
+        </is>
+      </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="B60" t="n">
         <v>4112</v>
@@ -4107,8 +4589,10 @@
       <c r="C60" t="n">
         <v>4112</v>
       </c>
-      <c r="D60" t="n">
-        <v>85</v>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -4128,10 +4612,10 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="n">
-        <v>35.00889415470556</v>
+        <v>0.4697</v>
       </c>
       <c r="K60" t="n">
-        <v>-25.57</v>
+        <v>-25.64</v>
       </c>
       <c r="L60" t="n">
         <v>2.34953594498787</v>
@@ -4150,18 +4634,26 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R60" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>p85-4112</t>
+        </is>
+      </c>
+      <c r="S60" t="n">
         <v>4112</v>
       </c>
-      <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="n">
+        <v>0.4697</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="B61" t="n">
         <v>8072</v>
@@ -4169,8 +4661,10 @@
       <c r="C61" t="n">
         <v>4115</v>
       </c>
-      <c r="D61" t="n">
-        <v>85</v>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -4212,18 +4706,24 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R61" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>p85-8072</t>
+        </is>
+      </c>
+      <c r="S61" t="n">
         <v>8072</v>
       </c>
-      <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="B62" t="n">
         <v>4240</v>
@@ -4231,8 +4731,10 @@
       <c r="C62" t="n">
         <v>4240</v>
       </c>
-      <c r="D62" t="n">
-        <v>83</v>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -4274,18 +4776,24 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R62" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>p83-4240</t>
+        </is>
+      </c>
+      <c r="S62" t="n">
         <v>4240</v>
       </c>
-      <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="B63" t="n">
         <v>4241</v>
@@ -4293,8 +4801,10 @@
       <c r="C63" t="n">
         <v>4241</v>
       </c>
-      <c r="D63" t="n">
-        <v>83</v>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -4336,18 +4846,24 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R63" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>p83-4241</t>
+        </is>
+      </c>
+      <c r="S63" t="n">
         <v>4241</v>
       </c>
-      <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="B64" t="n">
         <v>4242</v>
@@ -4355,8 +4871,10 @@
       <c r="C64" t="n">
         <v>4242</v>
       </c>
-      <c r="D64" t="n">
-        <v>83</v>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -4398,18 +4916,24 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R64" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>p83-4242</t>
+        </is>
+      </c>
+      <c r="S64" t="n">
         <v>4242</v>
       </c>
-      <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="B65" t="n">
         <v>8068</v>
@@ -4417,8 +4941,10 @@
       <c r="C65" t="n">
         <v>4244</v>
       </c>
-      <c r="D65" t="n">
-        <v>83</v>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -4460,18 +4986,24 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R65" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>p83-8068</t>
+        </is>
+      </c>
+      <c r="S65" t="n">
         <v>8068</v>
       </c>
-      <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="B66" t="n">
         <v>4248</v>
@@ -4479,8 +5011,10 @@
       <c r="C66" t="n">
         <v>4248</v>
       </c>
-      <c r="D66" t="n">
-        <v>83</v>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -4522,18 +5056,24 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R66" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>p83-4248</t>
+        </is>
+      </c>
+      <c r="S66" t="n">
         <v>4248</v>
       </c>
-      <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="B67" t="n">
         <v>4249</v>
@@ -4541,8 +5081,10 @@
       <c r="C67" t="n">
         <v>4249</v>
       </c>
-      <c r="D67" t="n">
-        <v>83</v>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -4584,18 +5126,24 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R67" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>p83-4249</t>
+        </is>
+      </c>
+      <c r="S67" t="n">
         <v>4249</v>
       </c>
-      <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="B68" t="n">
         <v>4250</v>
@@ -4603,8 +5151,10 @@
       <c r="C68" t="n">
         <v>4250</v>
       </c>
-      <c r="D68" t="n">
-        <v>83</v>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -4646,25 +5196,33 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R68" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>p83-4250</t>
+        </is>
+      </c>
+      <c r="S68" t="n">
         <v>4250</v>
       </c>
-      <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="B69" t="n">
         <v>8023</v>
       </c>
       <c r="C69" t="inlineStr"/>
-      <c r="D69" t="n">
-        <v>81</v>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -4706,25 +5264,33 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R69" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>p81-8023</t>
+        </is>
+      </c>
+      <c r="S69" t="n">
         <v>8023</v>
       </c>
-      <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="B70" t="n">
         <v>8034</v>
       </c>
       <c r="C70" t="inlineStr"/>
-      <c r="D70" t="n">
-        <v>81</v>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -4766,25 +5332,33 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R70" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>p81-8034</t>
+        </is>
+      </c>
+      <c r="S70" t="n">
         <v>8034</v>
       </c>
-      <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="B71" t="n">
         <v>8056</v>
       </c>
       <c r="C71" t="inlineStr"/>
-      <c r="D71" t="n">
-        <v>81</v>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -4826,25 +5400,33 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R71" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>p81-8056</t>
+        </is>
+      </c>
+      <c r="S71" t="n">
         <v>8056</v>
       </c>
-      <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B72" t="n">
         <v>8035</v>
       </c>
       <c r="C72" t="inlineStr"/>
-      <c r="D72" t="n">
-        <v>81</v>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -4886,25 +5468,33 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R72" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>p81-8035</t>
+        </is>
+      </c>
+      <c r="S72" t="n">
         <v>8035</v>
       </c>
-      <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="B73" t="n">
         <v>8073</v>
       </c>
       <c r="C73" t="inlineStr"/>
-      <c r="D73" t="n">
-        <v>85</v>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -4946,18 +5536,24 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R73" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>p85-8073</t>
+        </is>
+      </c>
+      <c r="S73" t="n">
         <v>8073</v>
       </c>
-      <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="B74" t="n">
         <v>8203</v>
@@ -4965,8 +5561,10 @@
       <c r="C74" t="n">
         <v>143</v>
       </c>
-      <c r="D74" t="n">
-        <v>6</v>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -5008,18 +5606,24 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R74" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>p06-8203</t>
+        </is>
+      </c>
+      <c r="S74" t="n">
         <v>8203</v>
       </c>
-      <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="B75" t="n">
         <v>8181</v>
@@ -5027,8 +5631,10 @@
       <c r="C75" t="n">
         <v>148</v>
       </c>
-      <c r="D75" t="n">
-        <v>6</v>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -5070,18 +5676,24 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R75" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>p06-8181</t>
+        </is>
+      </c>
+      <c r="S75" t="n">
         <v>8181</v>
       </c>
-      <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="B76" t="n">
         <v>8200</v>
@@ -5089,8 +5701,10 @@
       <c r="C76" t="n">
         <v>169</v>
       </c>
-      <c r="D76" t="n">
-        <v>6</v>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -5132,18 +5746,24 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R76" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>p06-8200</t>
+        </is>
+      </c>
+      <c r="S76" t="n">
         <v>8200</v>
       </c>
-      <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="B77" t="n">
         <v>8200</v>
@@ -5151,8 +5771,10 @@
       <c r="C77" t="n">
         <v>169</v>
       </c>
-      <c r="D77" t="n">
-        <v>6</v>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -5194,18 +5816,24 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R77" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>p06-8200</t>
+        </is>
+      </c>
+      <c r="S77" t="n">
         <v>8200</v>
       </c>
-      <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="B78" t="n">
         <v>8150</v>
@@ -5213,8 +5841,10 @@
       <c r="C78" t="n">
         <v>183</v>
       </c>
-      <c r="D78" t="n">
-        <v>7</v>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -5256,18 +5886,24 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R78" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>p07-8150</t>
+        </is>
+      </c>
+      <c r="S78" t="n">
         <v>8150</v>
       </c>
-      <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="B79" t="n">
         <v>8149</v>
@@ -5275,8 +5911,10 @@
       <c r="C79" t="n">
         <v>184</v>
       </c>
-      <c r="D79" t="n">
-        <v>7</v>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -5296,10 +5934,10 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="n">
-        <v>35.35182591438389</v>
+        <v>0.4372</v>
       </c>
       <c r="K79" t="n">
-        <v>-29.07</v>
+        <v>-29.34</v>
       </c>
       <c r="L79" t="n">
         <v>2.75667756446349</v>
@@ -5318,18 +5956,26 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R79" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>p07-8149</t>
+        </is>
+      </c>
+      <c r="S79" t="n">
         <v>8149</v>
       </c>
-      <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="n">
+        <v>0.4372</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="B80" t="n">
         <v>8152</v>
@@ -5337,8 +5983,10 @@
       <c r="C80" t="n">
         <v>191</v>
       </c>
-      <c r="D80" t="n">
-        <v>7</v>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -5380,18 +6028,24 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R80" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>p07-8152</t>
+        </is>
+      </c>
+      <c r="S80" t="n">
         <v>8152</v>
       </c>
-      <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="B81" t="n">
         <v>8158</v>
@@ -5399,8 +6053,10 @@
       <c r="C81" t="n">
         <v>199</v>
       </c>
-      <c r="D81" t="n">
-        <v>7</v>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -5442,18 +6098,24 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R81" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>p07-8158</t>
+        </is>
+      </c>
+      <c r="S81" t="n">
         <v>8158</v>
       </c>
-      <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="B82" t="n">
         <v>8140</v>
@@ -5461,8 +6123,10 @@
       <c r="C82" t="n">
         <v>202</v>
       </c>
-      <c r="D82" t="n">
-        <v>8</v>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -5504,18 +6168,24 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R82" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>p08-8140</t>
+        </is>
+      </c>
+      <c r="S82" t="n">
         <v>8140</v>
       </c>
-      <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="B83" t="n">
         <v>8130</v>
@@ -5523,8 +6193,10 @@
       <c r="C83" t="n">
         <v>203</v>
       </c>
-      <c r="D83" t="n">
-        <v>8</v>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -5566,18 +6238,24 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R83" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>p08-8130</t>
+        </is>
+      </c>
+      <c r="S83" t="n">
         <v>8130</v>
       </c>
-      <c r="S83" t="inlineStr"/>
       <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="B84" t="n">
         <v>8132</v>
@@ -5585,8 +6263,10 @@
       <c r="C84" t="n">
         <v>208</v>
       </c>
-      <c r="D84" t="n">
-        <v>8</v>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -5628,18 +6308,24 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R84" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>p08-8132</t>
+        </is>
+      </c>
+      <c r="S84" t="n">
         <v>8132</v>
       </c>
-      <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="B85" t="n">
         <v>8141</v>
@@ -5647,8 +6333,10 @@
       <c r="C85" t="n">
         <v>210</v>
       </c>
-      <c r="D85" t="n">
-        <v>8</v>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -5690,18 +6378,24 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R85" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>p08-8141</t>
+        </is>
+      </c>
+      <c r="S85" t="n">
         <v>8141</v>
       </c>
-      <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="B86" t="n">
         <v>8139</v>
@@ -5709,8 +6403,10 @@
       <c r="C86" t="n">
         <v>212</v>
       </c>
-      <c r="D86" t="n">
-        <v>8</v>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -5752,18 +6448,24 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R86" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>p08-8139</t>
+        </is>
+      </c>
+      <c r="S86" t="n">
         <v>8139</v>
       </c>
-      <c r="S86" t="inlineStr"/>
       <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="B87" t="n">
         <v>8107</v>
@@ -5771,8 +6473,10 @@
       <c r="C87" t="n">
         <v>1643</v>
       </c>
-      <c r="D87" t="n">
-        <v>55</v>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -5814,18 +6518,24 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R87" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>p55-8107</t>
+        </is>
+      </c>
+      <c r="S87" t="n">
         <v>8107</v>
       </c>
-      <c r="S87" t="inlineStr"/>
       <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="B88" t="n">
         <v>8124</v>
@@ -5833,8 +6543,10 @@
       <c r="C88" t="n">
         <v>1647</v>
       </c>
-      <c r="D88" t="n">
-        <v>55</v>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -5876,18 +6588,24 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R88" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>p55-8124</t>
+        </is>
+      </c>
+      <c r="S88" t="n">
         <v>8124</v>
       </c>
-      <c r="S88" t="inlineStr"/>
       <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="B89" t="n">
         <v>8106</v>
@@ -5895,8 +6613,10 @@
       <c r="C89" t="n">
         <v>1678</v>
       </c>
-      <c r="D89" t="n">
-        <v>55</v>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -5938,25 +6658,33 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R89" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>p55-8106</t>
+        </is>
+      </c>
+      <c r="S89" t="n">
         <v>8106</v>
       </c>
-      <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="B90" t="n">
         <v>8154</v>
       </c>
       <c r="C90" t="inlineStr"/>
-      <c r="D90" t="n">
-        <v>7</v>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -5976,10 +6704,10 @@
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="n">
-        <v>46.84</v>
+        <v>0.4506</v>
       </c>
       <c r="K90" t="n">
-        <v>-30.02</v>
+        <v>-30.01</v>
       </c>
       <c r="L90" t="n">
         <v>2.45034469589428</v>
@@ -5998,22 +6726,34 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R90" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>p07-8154</t>
+        </is>
+      </c>
+      <c r="S90" t="n">
         <v>8154</v>
       </c>
-      <c r="S90" t="inlineStr"/>
       <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="n">
+        <v>0.4506</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>&lt;NA&gt;</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
@@ -6034,22 +6774,32 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R91" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>p&lt;NA&gt;-&lt;NA&gt;</t>
+        </is>
+      </c>
+      <c r="S91" t="n">
         <v>4038.1</v>
       </c>
-      <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>&lt;NA&gt;</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
@@ -6070,18 +6820,24 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>pulverized</t>
-        </is>
-      </c>
-      <c r="R92" t="n">
+          <t>leaf pulverized</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>p&lt;NA&gt;-&lt;NA&gt;</t>
+        </is>
+      </c>
+      <c r="S92" t="n">
         <v>4038.2</v>
       </c>
-      <c r="S92" t="inlineStr"/>
       <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="B93" t="n">
         <v>8186</v>
@@ -6137,13 +6893,19 @@
           <t>herbarium</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr"/>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>p06-1689.0</t>
+        </is>
+      </c>
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="B94" t="n">
         <v>8182</v>
@@ -6199,13 +6961,19 @@
           <t>herbarium</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr"/>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>p06-1711.0</t>
+        </is>
+      </c>
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="B95" t="n">
         <v>8147</v>
@@ -6261,13 +7029,19 @@
           <t>herbarium</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr"/>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>p07-1715.0</t>
+        </is>
+      </c>
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="B96" t="n">
         <v>8151</v>
@@ -6323,13 +7097,19 @@
           <t>herbarium</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr"/>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>p07-1738.0</t>
+        </is>
+      </c>
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c r="B97" t="n">
         <v>8120</v>
@@ -6385,13 +7165,19 @@
           <t>herbarium</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr"/>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>p55-3150.0</t>
+        </is>
+      </c>
       <c r="S97" t="inlineStr"/>
       <c r="T97" t="inlineStr"/>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>5</v>
+        <v>96</v>
       </c>
       <c r="B98" t="n">
         <v>8123</v>
@@ -6447,13 +7233,19 @@
           <t>herbarium</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr"/>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>p55-3151.0</t>
+        </is>
+      </c>
       <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr"/>
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>6</v>
+        <v>97</v>
       </c>
       <c r="B99" t="n">
         <v>4039</v>
@@ -6509,13 +7301,19 @@
           <t>herbarium</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr"/>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>p82-4194.0</t>
+        </is>
+      </c>
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="B100" t="n">
         <v>8147</v>
@@ -6523,8 +7321,10 @@
       <c r="C100" t="n">
         <v>178</v>
       </c>
-      <c r="D100" t="n">
-        <v>7</v>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -6567,21 +7367,27 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
+          <t>p07-178</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
           <t>p7-178</t>
         </is>
       </c>
-      <c r="S100" t="n">
+      <c r="T100" t="n">
         <v>1940</v>
       </c>
-      <c r="T100" t="inlineStr">
+      <c r="U100" t="inlineStr">
         <is>
           <t>Chomelia tenuiflora</t>
         </is>
       </c>
+      <c r="V100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="B101" t="n">
         <v>8200</v>
@@ -6589,8 +7395,10 @@
       <c r="C101" t="n">
         <v>169</v>
       </c>
-      <c r="D101" t="n">
-        <v>6</v>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -6633,21 +7441,27 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
+          <t>p06-169</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
           <t>p6-169</t>
         </is>
       </c>
-      <c r="S101" t="n">
+      <c r="T101" t="n">
         <v>2000</v>
       </c>
-      <c r="T101" t="inlineStr">
+      <c r="U101" t="inlineStr">
         <is>
           <t>Critoniopsis cf occidentalis</t>
         </is>
       </c>
+      <c r="V101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="B102" t="n">
         <v>8141</v>
@@ -6655,8 +7469,10 @@
       <c r="C102" t="n">
         <v>210</v>
       </c>
-      <c r="D102" t="n">
-        <v>8</v>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -6699,28 +7515,36 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
+          <t>p08-210</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
           <t>p8-210</t>
         </is>
       </c>
-      <c r="S102" t="n">
+      <c r="T102" t="n">
         <v>1995</v>
       </c>
-      <c r="T102" t="inlineStr">
+      <c r="U102" t="inlineStr">
         <is>
           <t>Erythrina edulis</t>
         </is>
       </c>
+      <c r="V102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>3</v>
+        <v>101</v>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
         <v>185</v>
       </c>
-      <c r="D103" t="n">
-        <v>7</v>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -6763,19 +7587,25 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
+          <t>p07-185</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
           <t>p7-185</t>
         </is>
       </c>
-      <c r="S103" t="inlineStr"/>
-      <c r="T103" t="inlineStr">
+      <c r="T103" t="inlineStr"/>
+      <c r="U103" t="inlineStr">
         <is>
           <t>Joosia umbellifera</t>
         </is>
       </c>
+      <c r="V103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="B104" t="n">
         <v>8158</v>
@@ -6783,8 +7613,10 @@
       <c r="C104" t="n">
         <v>199</v>
       </c>
-      <c r="D104" t="n">
-        <v>7</v>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -6827,28 +7659,36 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
+          <t>p07-199</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
           <t>p7-199</t>
         </is>
       </c>
-      <c r="S104" t="n">
+      <c r="T104" t="n">
         <v>1940</v>
       </c>
-      <c r="T104" t="inlineStr">
+      <c r="U104" t="inlineStr">
         <is>
           <t>Joosia umbellifera</t>
         </is>
       </c>
+      <c r="V104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>5</v>
+        <v>103</v>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
         <v>200</v>
       </c>
-      <c r="D105" t="n">
-        <v>7</v>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -6891,19 +7731,25 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
+          <t>p07-200</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
           <t>p7-200</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr"/>
-      <c r="T105" t="inlineStr">
+      <c r="T105" t="inlineStr"/>
+      <c r="U105" t="inlineStr">
         <is>
           <t>Aniba cf coto</t>
         </is>
       </c>
+      <c r="V105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>6</v>
+        <v>104</v>
       </c>
       <c r="B106" t="n">
         <v>8130</v>
@@ -6911,8 +7757,10 @@
       <c r="C106" t="n">
         <v>203</v>
       </c>
-      <c r="D106" t="n">
-        <v>8</v>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -6955,28 +7803,36 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
+          <t>p08-203</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
           <t>p8-203</t>
         </is>
       </c>
-      <c r="S106" t="n">
+      <c r="T106" t="n">
         <v>1995</v>
       </c>
-      <c r="T106" t="inlineStr">
+      <c r="U106" t="inlineStr">
         <is>
           <t>Faramea oblongifolia</t>
         </is>
       </c>
+      <c r="V106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>7</v>
+        <v>105</v>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
         <v>179</v>
       </c>
-      <c r="D107" t="n">
-        <v>7</v>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -7019,19 +7875,25 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
+          <t>p07-179</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
           <t>p7-179</t>
         </is>
       </c>
-      <c r="S107" t="inlineStr"/>
-      <c r="T107" t="inlineStr">
+      <c r="T107" t="inlineStr"/>
+      <c r="U107" t="inlineStr">
         <is>
           <t>Tetrorchidium andinum</t>
         </is>
       </c>
+      <c r="V107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>8</v>
+        <v>106</v>
       </c>
       <c r="B108" t="n">
         <v>8133</v>
@@ -7039,8 +7901,10 @@
       <c r="C108" t="n">
         <v>209</v>
       </c>
-      <c r="D108" t="n">
-        <v>8</v>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -7083,21 +7947,27 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
+          <t>p08-209</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
           <t>p8-209</t>
         </is>
       </c>
-      <c r="S108" t="n">
+      <c r="T108" t="n">
         <v>1995</v>
       </c>
-      <c r="T108" t="inlineStr">
+      <c r="U108" t="inlineStr">
         <is>
           <t>Ruagea</t>
         </is>
       </c>
+      <c r="V108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>9</v>
+        <v>107</v>
       </c>
       <c r="B109" t="n">
         <v>8182</v>
@@ -7105,8 +7975,10 @@
       <c r="C109" t="n">
         <v>151</v>
       </c>
-      <c r="D109" t="n">
-        <v>6</v>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -7149,28 +8021,36 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
+          <t>p06-151</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
           <t>p6-151</t>
         </is>
       </c>
-      <c r="S109" t="n">
+      <c r="T109" t="n">
         <v>2000</v>
       </c>
-      <c r="T109" t="inlineStr">
+      <c r="U109" t="inlineStr">
         <is>
           <t>Posoqueria coriacea</t>
         </is>
       </c>
+      <c r="V109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>10</v>
+        <v>108</v>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="n">
         <v>181</v>
       </c>
-      <c r="D110" t="n">
-        <v>7</v>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -7203,17 +8083,23 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R110" t="inlineStr"/>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>p07-181</t>
+        </is>
+      </c>
       <c r="S110" t="inlineStr"/>
-      <c r="T110" t="inlineStr">
+      <c r="T110" t="inlineStr"/>
+      <c r="U110" t="inlineStr">
         <is>
           <t>Inga sp. 1</t>
         </is>
       </c>
+      <c r="V110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>11</v>
+        <v>109</v>
       </c>
       <c r="B111" t="n">
         <v>8181</v>
@@ -7221,8 +8107,10 @@
       <c r="C111" t="n">
         <v>148</v>
       </c>
-      <c r="D111" t="n">
-        <v>6</v>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -7265,21 +8153,27 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
+          <t>p06-148</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
           <t>p6-148</t>
         </is>
       </c>
-      <c r="S111" t="n">
+      <c r="T111" t="n">
         <v>2000</v>
       </c>
-      <c r="T111" t="inlineStr">
+      <c r="U111" t="inlineStr">
         <is>
           <t>Ficus tonduzii</t>
         </is>
       </c>
+      <c r="V111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>12</v>
+        <v>110</v>
       </c>
       <c r="B112" t="n">
         <v>8203</v>
@@ -7287,8 +8181,10 @@
       <c r="C112" t="n">
         <v>143</v>
       </c>
-      <c r="D112" t="n">
-        <v>6</v>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -7331,28 +8227,36 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
+          <t>p06-143</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
           <t>p6-143</t>
         </is>
       </c>
-      <c r="S112" t="n">
+      <c r="T112" t="n">
         <v>2000</v>
       </c>
-      <c r="T112" t="inlineStr">
+      <c r="U112" t="inlineStr">
         <is>
           <t>Weinmannia pinnata</t>
         </is>
       </c>
+      <c r="V112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
         <v>142</v>
       </c>
-      <c r="D113" t="n">
-        <v>6</v>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -7395,26 +8299,34 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
+          <t>p06-142</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
           <t>p6-142</t>
         </is>
       </c>
-      <c r="S113" t="inlineStr"/>
-      <c r="T113" t="inlineStr">
+      <c r="T113" t="inlineStr"/>
+      <c r="U113" t="inlineStr">
         <is>
           <t>Palicourea stenosepala</t>
         </is>
       </c>
+      <c r="V113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>14</v>
+        <v>112</v>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="n">
         <v>182</v>
       </c>
-      <c r="D114" t="n">
-        <v>7</v>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -7457,19 +8369,25 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
+          <t>p07-182</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
           <t>p7-182</t>
         </is>
       </c>
-      <c r="S114" t="inlineStr"/>
-      <c r="T114" t="inlineStr">
+      <c r="T114" t="inlineStr"/>
+      <c r="U114" t="inlineStr">
         <is>
           <t>Endlicheria griseo-sericea</t>
         </is>
       </c>
+      <c r="V114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>15</v>
+        <v>113</v>
       </c>
       <c r="B115" t="n">
         <v>8188</v>
@@ -7477,8 +8395,10 @@
       <c r="C115" t="n">
         <v>158</v>
       </c>
-      <c r="D115" t="n">
-        <v>6</v>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -7521,21 +8441,27 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
+          <t>p06-158</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
           <t>p6-158</t>
         </is>
       </c>
-      <c r="S115" t="n">
+      <c r="T115" t="n">
         <v>2000</v>
       </c>
-      <c r="T115" t="inlineStr">
+      <c r="U115" t="inlineStr">
         <is>
           <t xml:space="preserve"> sp. 1</t>
         </is>
       </c>
+      <c r="V115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>16</v>
+        <v>114</v>
       </c>
       <c r="B116" t="n">
         <v>8188</v>
@@ -7543,8 +8469,10 @@
       <c r="C116" t="n">
         <v>158</v>
       </c>
-      <c r="D116" t="n">
-        <v>6</v>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -7587,28 +8515,36 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
+          <t>p06-158</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
           <t>p6-158</t>
         </is>
       </c>
-      <c r="S116" t="n">
+      <c r="T116" t="n">
         <v>2000</v>
       </c>
-      <c r="T116" t="inlineStr">
+      <c r="U116" t="inlineStr">
         <is>
           <t xml:space="preserve"> sp. 1</t>
         </is>
       </c>
+      <c r="V116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>17</v>
+        <v>115</v>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
         <v>160</v>
       </c>
-      <c r="D117" t="n">
-        <v>6</v>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -7651,19 +8587,25 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
+          <t>p06-160</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
           <t>p6-160</t>
         </is>
       </c>
-      <c r="S117" t="inlineStr"/>
-      <c r="T117" t="inlineStr">
+      <c r="T117" t="inlineStr"/>
+      <c r="U117" t="inlineStr">
         <is>
           <t>Palicourea stenosepala</t>
         </is>
       </c>
+      <c r="V117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>18</v>
+        <v>116</v>
       </c>
       <c r="B118" t="n">
         <v>8194</v>
@@ -7671,8 +8613,10 @@
       <c r="C118" t="n">
         <v>161</v>
       </c>
-      <c r="D118" t="n">
-        <v>6</v>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -7715,28 +8659,36 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
+          <t>p06-161</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
           <t>p6-161</t>
         </is>
       </c>
-      <c r="S118" t="n">
+      <c r="T118" t="n">
         <v>2000</v>
       </c>
-      <c r="T118" t="inlineStr">
+      <c r="U118" t="inlineStr">
         <is>
           <t>Guarea kunthiana</t>
         </is>
       </c>
+      <c r="V118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
         <v>190</v>
       </c>
-      <c r="D119" t="n">
-        <v>7</v>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -7779,19 +8731,25 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
+          <t>p07-190</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
           <t>p7-190</t>
         </is>
       </c>
-      <c r="S119" t="inlineStr"/>
-      <c r="T119" t="inlineStr">
+      <c r="T119" t="inlineStr"/>
+      <c r="U119" t="inlineStr">
         <is>
           <t>Joosia umbellifera</t>
         </is>
       </c>
+      <c r="V119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>20</v>
+        <v>118</v>
       </c>
       <c r="B120" t="n">
         <v>8151</v>
@@ -7799,8 +8757,10 @@
       <c r="C120" t="n">
         <v>186</v>
       </c>
-      <c r="D120" t="n">
-        <v>7</v>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -7833,19 +8793,25 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R120" t="inlineStr"/>
-      <c r="S120" t="n">
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>p07-186</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" t="n">
         <v>1940</v>
       </c>
-      <c r="T120" t="inlineStr">
+      <c r="U120" t="inlineStr">
         <is>
           <t>Elaeagia cf utilis</t>
         </is>
       </c>
+      <c r="V120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="B121" t="n">
         <v>8132</v>
@@ -7853,8 +8819,10 @@
       <c r="C121" t="n">
         <v>208</v>
       </c>
-      <c r="D121" t="n">
-        <v>8</v>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -7897,28 +8865,36 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
+          <t>p08-208</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
           <t>p8-208</t>
         </is>
       </c>
-      <c r="S121" t="n">
+      <c r="T121" t="n">
         <v>1995</v>
       </c>
-      <c r="T121" t="inlineStr">
+      <c r="U121" t="inlineStr">
         <is>
           <t>Hyeronima sp 2 cf macrocarpa</t>
         </is>
       </c>
+      <c r="V121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="n">
         <v>223</v>
       </c>
-      <c r="D122" t="n">
-        <v>8</v>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -7961,19 +8937,25 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
+          <t>p08-223</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
           <t>p8-223</t>
         </is>
       </c>
-      <c r="S122" t="inlineStr"/>
-      <c r="T122" t="inlineStr">
+      <c r="T122" t="inlineStr"/>
+      <c r="U122" t="inlineStr">
         <is>
           <t>Calatola costaricensis</t>
         </is>
       </c>
+      <c r="V122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>23</v>
+        <v>121</v>
       </c>
       <c r="B123" t="n">
         <v>8136</v>
@@ -7981,8 +8963,10 @@
       <c r="C123" t="n">
         <v>218</v>
       </c>
-      <c r="D123" t="n">
-        <v>8</v>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -8025,21 +9009,27 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
+          <t>p08-218</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
           <t>p8-218</t>
         </is>
       </c>
-      <c r="S123" t="n">
+      <c r="T123" t="n">
         <v>1995</v>
       </c>
-      <c r="T123" t="inlineStr">
+      <c r="U123" t="inlineStr">
         <is>
           <t>Miconia glandulistyla</t>
         </is>
       </c>
+      <c r="V123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="B124" t="n">
         <v>8136</v>
@@ -8047,8 +9037,10 @@
       <c r="C124" t="n">
         <v>218</v>
       </c>
-      <c r="D124" t="n">
-        <v>8</v>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -8091,28 +9083,36 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
+          <t>p08-218</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
           <t>p8-218</t>
         </is>
       </c>
-      <c r="S124" t="n">
+      <c r="T124" t="n">
         <v>1995</v>
       </c>
-      <c r="T124" t="inlineStr">
+      <c r="U124" t="inlineStr">
         <is>
           <t>Miconia glandulistyla</t>
         </is>
       </c>
+      <c r="V124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="n">
         <v>222</v>
       </c>
-      <c r="D125" t="n">
-        <v>8</v>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -8155,19 +9155,25 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
+          <t>p08-222</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
           <t>p8-222</t>
         </is>
       </c>
-      <c r="S125" t="inlineStr"/>
-      <c r="T125" t="inlineStr">
+      <c r="T125" t="inlineStr"/>
+      <c r="U125" t="inlineStr">
         <is>
           <t>Allophylus floribundus</t>
         </is>
       </c>
+      <c r="V125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>26</v>
+        <v>124</v>
       </c>
       <c r="B126" t="n">
         <v>8122</v>
@@ -8175,8 +9181,10 @@
       <c r="C126" t="n">
         <v>1649</v>
       </c>
-      <c r="D126" t="n">
-        <v>55</v>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -8222,18 +9230,24 @@
           <t>p55-1649</t>
         </is>
       </c>
-      <c r="S126" t="n">
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>p55-1649</t>
+        </is>
+      </c>
+      <c r="T126" t="n">
         <v>2000</v>
       </c>
-      <c r="T126" t="inlineStr">
+      <c r="U126" t="inlineStr">
         <is>
           <t xml:space="preserve">Ruagea </t>
         </is>
       </c>
+      <c r="V126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>27</v>
+        <v>125</v>
       </c>
       <c r="B127" t="n">
         <v>8123</v>
@@ -8241,8 +9255,10 @@
       <c r="C127" t="n">
         <v>1648</v>
       </c>
-      <c r="D127" t="n">
-        <v>55</v>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -8288,24 +9304,34 @@
           <t>p55-1648</t>
         </is>
       </c>
-      <c r="S127" t="n">
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>p55-1648</t>
+        </is>
+      </c>
+      <c r="T127" t="n">
         <v>2000</v>
       </c>
-      <c r="T127" t="inlineStr">
+      <c r="U127" t="inlineStr">
         <is>
           <t>Hedyosmum cuatrecazanum</t>
         </is>
       </c>
+      <c r="V127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
         <v>472</v>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>&lt;NA&gt;</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>Guacamayos</t>
@@ -8333,20 +9359,28 @@
           <t>leaf pulverized</t>
         </is>
       </c>
-      <c r="R128" t="inlineStr"/>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>p&lt;NA&gt;-472</t>
+        </is>
+      </c>
       <c r="S128" t="inlineStr"/>
       <c r="T128" t="inlineStr"/>
+      <c r="U128" t="inlineStr"/>
+      <c r="V128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>29</v>
+        <v>127</v>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="n">
         <v>1666</v>
       </c>
-      <c r="D129" t="n">
-        <v>55</v>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -8392,23 +9426,31 @@
           <t>p55-1666</t>
         </is>
       </c>
-      <c r="S129" t="inlineStr"/>
-      <c r="T129" t="inlineStr">
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>p55-1666</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr"/>
+      <c r="U129" t="inlineStr">
         <is>
           <t>Palicourea corniculata</t>
         </is>
       </c>
+      <c r="V129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>30</v>
+        <v>128</v>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="n">
         <v>1659</v>
       </c>
-      <c r="D130" t="n">
-        <v>55</v>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -8454,16 +9496,22 @@
           <t>p55-1659</t>
         </is>
       </c>
-      <c r="S130" t="inlineStr"/>
-      <c r="T130" t="inlineStr">
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>p55-1659</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr"/>
+      <c r="U130" t="inlineStr">
         <is>
           <t>Cybianthus occigranatensis</t>
         </is>
       </c>
+      <c r="V130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="B131" t="n">
         <v>8106</v>
@@ -8471,8 +9519,10 @@
       <c r="C131" t="n">
         <v>1678</v>
       </c>
-      <c r="D131" t="n">
-        <v>55</v>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -8518,25 +9568,33 @@
           <t>p55-1678</t>
         </is>
       </c>
-      <c r="S131" t="n">
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>p55-1678</t>
+        </is>
+      </c>
+      <c r="T131" t="n">
         <v>2000</v>
       </c>
-      <c r="T131" t="inlineStr">
+      <c r="U131" t="inlineStr">
         <is>
           <t>Faramea oblongifolia</t>
         </is>
       </c>
+      <c r="V131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="n">
         <v>206</v>
       </c>
-      <c r="D132" t="n">
-        <v>8</v>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -8579,26 +9637,34 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
+          <t>p08-206</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
           <t>p8-206</t>
         </is>
       </c>
-      <c r="S132" t="inlineStr"/>
-      <c r="T132" t="inlineStr">
+      <c r="T132" t="inlineStr"/>
+      <c r="U132" t="inlineStr">
         <is>
           <t>Palicourea cf andrei</t>
         </is>
       </c>
+      <c r="V132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>33</v>
+        <v>131</v>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="n">
         <v>1653</v>
       </c>
-      <c r="D133" t="n">
-        <v>55</v>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -8644,16 +9710,22 @@
           <t>p55-1653</t>
         </is>
       </c>
-      <c r="S133" t="inlineStr"/>
-      <c r="T133" t="inlineStr">
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>p55-1653</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr"/>
+      <c r="U133" t="inlineStr">
         <is>
           <t>Saurauia sp. 1</t>
         </is>
       </c>
+      <c r="V133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>34</v>
+        <v>132</v>
       </c>
       <c r="B134" t="n">
         <v>8139</v>
@@ -8661,8 +9733,10 @@
       <c r="C134" t="n">
         <v>212</v>
       </c>
-      <c r="D134" t="n">
-        <v>8</v>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -8705,28 +9779,36 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
+          <t>p08-212</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
           <t>p8-212</t>
         </is>
       </c>
-      <c r="S134" t="n">
+      <c r="T134" t="n">
         <v>1995</v>
       </c>
-      <c r="T134" t="inlineStr">
+      <c r="U134" t="inlineStr">
         <is>
           <t>Weinmannia pinnata</t>
         </is>
       </c>
+      <c r="V134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>35</v>
+        <v>133</v>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="n">
         <v>168</v>
       </c>
-      <c r="D135" t="n">
-        <v>6</v>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -8769,26 +9851,34 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
+          <t>p06-168</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
           <t>p6-168</t>
         </is>
       </c>
-      <c r="S135" t="inlineStr"/>
-      <c r="T135" t="inlineStr">
+      <c r="T135" t="inlineStr"/>
+      <c r="U135" t="inlineStr">
         <is>
           <t>Palicourea stenosepala</t>
         </is>
       </c>
+      <c r="V135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>36</v>
+        <v>134</v>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="n">
         <v>1654</v>
       </c>
-      <c r="D136" t="n">
-        <v>55</v>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -8834,16 +9924,22 @@
           <t>p55-1654</t>
         </is>
       </c>
-      <c r="S136" t="inlineStr"/>
-      <c r="T136" t="inlineStr">
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>p55-1654</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr"/>
+      <c r="U136" t="inlineStr">
         <is>
           <t>Faramea oblongifolia</t>
         </is>
       </c>
+      <c r="V136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>37</v>
+        <v>135</v>
       </c>
       <c r="B137" t="n">
         <v>8135</v>
@@ -8851,8 +9947,10 @@
       <c r="C137" t="n">
         <v>214</v>
       </c>
-      <c r="D137" t="n">
-        <v>8</v>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -8895,28 +9993,36 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
+          <t>p08-214</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
           <t>p8-214</t>
         </is>
       </c>
-      <c r="S137" t="n">
+      <c r="T137" t="n">
         <v>1995</v>
       </c>
-      <c r="T137" t="inlineStr">
+      <c r="U137" t="inlineStr">
         <is>
           <t>Cryptocarya aschersoniana</t>
         </is>
       </c>
+      <c r="V137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>38</v>
+        <v>136</v>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="n">
         <v>1645</v>
       </c>
-      <c r="D138" t="n">
-        <v>55</v>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -8962,23 +10068,31 @@
           <t>p55-1645</t>
         </is>
       </c>
-      <c r="S138" t="inlineStr"/>
-      <c r="T138" t="inlineStr">
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>p55-1645</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr"/>
+      <c r="U138" t="inlineStr">
         <is>
           <t>Palicourea stenosepala</t>
         </is>
       </c>
+      <c r="V138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>39</v>
+        <v>137</v>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
         <v>1672</v>
       </c>
-      <c r="D139" t="n">
-        <v>55</v>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -9024,23 +10138,31 @@
           <t>p55-1672</t>
         </is>
       </c>
-      <c r="S139" t="inlineStr"/>
-      <c r="T139" t="inlineStr">
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>p55-1672</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr"/>
+      <c r="U139" t="inlineStr">
         <is>
           <t>Saurauia sp. 1</t>
         </is>
       </c>
+      <c r="V139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>40</v>
+        <v>138</v>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="n">
         <v>183</v>
       </c>
-      <c r="D140" t="n">
-        <v>7</v>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -9083,26 +10205,34 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
+          <t>p07-183</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
           <t>p7-183</t>
         </is>
       </c>
-      <c r="S140" t="inlineStr"/>
-      <c r="T140" t="inlineStr">
+      <c r="T140" t="inlineStr"/>
+      <c r="U140" t="inlineStr">
         <is>
           <t>Joosia umbellifera</t>
         </is>
       </c>
+      <c r="V140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>41</v>
+        <v>139</v>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="n">
         <v>183</v>
       </c>
-      <c r="D141" t="n">
-        <v>7</v>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -9145,26 +10275,34 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
+          <t>p07-183</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
           <t>p7-183-a</t>
         </is>
       </c>
-      <c r="S141" t="inlineStr"/>
-      <c r="T141" t="inlineStr">
+      <c r="T141" t="inlineStr"/>
+      <c r="U141" t="inlineStr">
         <is>
           <t>Joosia umbellifera</t>
         </is>
       </c>
+      <c r="V141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="n">
         <v>183</v>
       </c>
-      <c r="D142" t="n">
-        <v>7</v>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -9207,19 +10345,25 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
+          <t>p07-183</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
           <t>p7-183-c</t>
         </is>
       </c>
-      <c r="S142" t="inlineStr"/>
-      <c r="T142" t="inlineStr">
+      <c r="T142" t="inlineStr"/>
+      <c r="U142" t="inlineStr">
         <is>
           <t>Joosia umbellifera</t>
         </is>
       </c>
+      <c r="V142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>43</v>
+        <v>141</v>
       </c>
       <c r="B143" t="n">
         <v>8186</v>
@@ -9227,8 +10371,10 @@
       <c r="C143" t="n">
         <v>157</v>
       </c>
-      <c r="D143" t="n">
-        <v>6</v>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -9243,8 +10389,12 @@
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
+      <c r="J143" t="n">
+        <v>0.4292</v>
+      </c>
+      <c r="K143" t="n">
+        <v>-28.53</v>
+      </c>
       <c r="L143" t="n">
         <v>0.03645078452623074</v>
       </c>
@@ -9263,28 +10413,38 @@
       <c r="Q143" t="inlineStr"/>
       <c r="R143" t="inlineStr">
         <is>
+          <t>p06-157</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
           <t>p6-157</t>
         </is>
       </c>
-      <c r="S143" t="n">
+      <c r="T143" t="n">
         <v>2000</v>
       </c>
-      <c r="T143" t="inlineStr">
+      <c r="U143" t="inlineStr">
         <is>
           <t>Sapium stylare</t>
         </is>
+      </c>
+      <c r="V143" t="n">
+        <v>0.4292</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>44</v>
+        <v>142</v>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="n">
         <v>669</v>
       </c>
-      <c r="D144" t="n">
-        <v>27</v>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -9299,8 +10459,12 @@
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
+      <c r="J144" t="n">
+        <v>0.4143</v>
+      </c>
+      <c r="K144" t="n">
+        <v>-29.16</v>
+      </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
@@ -9309,24 +10473,34 @@
         <v>2006</v>
       </c>
       <c r="Q144" t="inlineStr"/>
-      <c r="R144" t="inlineStr"/>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>p27-669</t>
+        </is>
+      </c>
       <c r="S144" t="inlineStr"/>
-      <c r="T144" t="inlineStr">
+      <c r="T144" t="inlineStr"/>
+      <c r="U144" t="inlineStr">
         <is>
           <t>Ruagea cf ovalis</t>
         </is>
+      </c>
+      <c r="V144" t="n">
+        <v>0.4143</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>45</v>
+        <v>143</v>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="n">
         <v>682</v>
       </c>
-      <c r="D145" t="n">
-        <v>27</v>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -9341,8 +10515,12 @@
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
+      <c r="J145" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="K145" t="n">
+        <v>-30.45</v>
+      </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
@@ -9351,24 +10529,34 @@
         <v>2006</v>
       </c>
       <c r="Q145" t="inlineStr"/>
-      <c r="R145" t="inlineStr"/>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>p27-682</t>
+        </is>
+      </c>
       <c r="S145" t="inlineStr"/>
-      <c r="T145" t="inlineStr">
+      <c r="T145" t="inlineStr"/>
+      <c r="U145" t="inlineStr">
         <is>
           <t>Ruagea cf ovalis</t>
         </is>
+      </c>
+      <c r="V145" t="n">
+        <v>0.3834</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46</v>
+        <v>144</v>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="n">
         <v>687</v>
       </c>
-      <c r="D146" t="n">
-        <v>27</v>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -9383,8 +10571,12 @@
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
+      <c r="J146" t="n">
+        <v>0.4476</v>
+      </c>
+      <c r="K146" t="n">
+        <v>-31.23</v>
+      </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr"/>
@@ -9393,24 +10585,34 @@
         <v>2006</v>
       </c>
       <c r="Q146" t="inlineStr"/>
-      <c r="R146" t="inlineStr"/>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>p27-687</t>
+        </is>
+      </c>
       <c r="S146" t="inlineStr"/>
-      <c r="T146" t="inlineStr">
+      <c r="T146" t="inlineStr"/>
+      <c r="U146" t="inlineStr">
         <is>
           <t xml:space="preserve">Margaritaria </t>
         </is>
+      </c>
+      <c r="V146" t="n">
+        <v>0.4476</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>47</v>
+        <v>145</v>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="n">
         <v>694</v>
       </c>
-      <c r="D147" t="n">
-        <v>27</v>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -9425,8 +10627,12 @@
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
+      <c r="J147" t="n">
+        <v>0.4236</v>
+      </c>
+      <c r="K147" t="n">
+        <v>-28.27</v>
+      </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
@@ -9435,24 +10641,34 @@
         <v>2006</v>
       </c>
       <c r="Q147" t="inlineStr"/>
-      <c r="R147" t="inlineStr"/>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>p27-694</t>
+        </is>
+      </c>
       <c r="S147" t="inlineStr"/>
-      <c r="T147" t="inlineStr">
+      <c r="T147" t="inlineStr"/>
+      <c r="U147" t="inlineStr">
         <is>
           <t>Joosia umbellifera</t>
         </is>
+      </c>
+      <c r="V147" t="n">
+        <v>0.4236</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>48</v>
+        <v>146</v>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
         <v>695</v>
       </c>
-      <c r="D148" t="n">
-        <v>27</v>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -9467,8 +10683,12 @@
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
+      <c r="J148" t="n">
+        <v>0.4182</v>
+      </c>
+      <c r="K148" t="n">
+        <v>-30.34</v>
+      </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
@@ -9477,24 +10697,34 @@
         <v>2006</v>
       </c>
       <c r="Q148" t="inlineStr"/>
-      <c r="R148" t="inlineStr"/>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>p27-695</t>
+        </is>
+      </c>
       <c r="S148" t="inlineStr"/>
-      <c r="T148" t="inlineStr">
+      <c r="T148" t="inlineStr"/>
+      <c r="U148" t="inlineStr">
         <is>
           <t>Joosia umbellifera</t>
         </is>
+      </c>
+      <c r="V148" t="n">
+        <v>0.4182</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>49</v>
+        <v>147</v>
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="n">
         <v>696</v>
       </c>
-      <c r="D149" t="n">
-        <v>27</v>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -9509,8 +10739,12 @@
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
+      <c r="J149" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="K149" t="n">
+        <v>-25.96</v>
+      </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr"/>
@@ -9519,24 +10753,34 @@
         <v>2006</v>
       </c>
       <c r="Q149" t="inlineStr"/>
-      <c r="R149" t="inlineStr"/>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>p27-696</t>
+        </is>
+      </c>
       <c r="S149" t="inlineStr"/>
-      <c r="T149" t="inlineStr">
+      <c r="T149" t="inlineStr"/>
+      <c r="U149" t="inlineStr">
         <is>
           <t xml:space="preserve">Elaeagia </t>
         </is>
+      </c>
+      <c r="V149" t="n">
+        <v>0.4183</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="n">
         <v>704</v>
       </c>
-      <c r="D150" t="n">
-        <v>27</v>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -9551,8 +10795,12 @@
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
+      <c r="J150" t="n">
+        <v>0.4218</v>
+      </c>
+      <c r="K150" t="n">
+        <v>-30.11</v>
+      </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
@@ -9561,24 +10809,34 @@
         <v>2006</v>
       </c>
       <c r="Q150" t="inlineStr"/>
-      <c r="R150" t="inlineStr"/>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>p27-704</t>
+        </is>
+      </c>
       <c r="S150" t="inlineStr"/>
-      <c r="T150" t="inlineStr">
+      <c r="T150" t="inlineStr"/>
+      <c r="U150" t="inlineStr">
         <is>
           <t>Palicourea cf andrei</t>
         </is>
+      </c>
+      <c r="V150" t="n">
+        <v>0.4218</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>51</v>
+        <v>149</v>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
         <v>708</v>
       </c>
-      <c r="D151" t="n">
-        <v>27</v>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -9593,8 +10851,12 @@
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
+      <c r="J151" t="n">
+        <v>0.4226</v>
+      </c>
+      <c r="K151" t="n">
+        <v>-30.48</v>
+      </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
@@ -9603,24 +10865,34 @@
         <v>2006</v>
       </c>
       <c r="Q151" t="inlineStr"/>
-      <c r="R151" t="inlineStr"/>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>p27-708</t>
+        </is>
+      </c>
       <c r="S151" t="inlineStr"/>
-      <c r="T151" t="inlineStr">
+      <c r="T151" t="inlineStr"/>
+      <c r="U151" t="inlineStr">
         <is>
           <t xml:space="preserve">Clethra fagifolia var fagifolia </t>
         </is>
+      </c>
+      <c r="V151" t="n">
+        <v>0.4226</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="n">
         <v>712</v>
       </c>
-      <c r="D152" t="n">
-        <v>27</v>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -9635,8 +10907,12 @@
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
+      <c r="J152" t="n">
+        <v>0.4231</v>
+      </c>
+      <c r="K152" t="n">
+        <v>-28.23</v>
+      </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
@@ -9645,24 +10921,34 @@
         <v>2006</v>
       </c>
       <c r="Q152" t="inlineStr"/>
-      <c r="R152" t="inlineStr"/>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>p27-712</t>
+        </is>
+      </c>
       <c r="S152" t="inlineStr"/>
-      <c r="T152" t="inlineStr">
+      <c r="T152" t="inlineStr"/>
+      <c r="U152" t="inlineStr">
         <is>
           <t>Pouteria baehniana</t>
         </is>
+      </c>
+      <c r="V152" t="n">
+        <v>0.4231</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>53</v>
+        <v>151</v>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="n">
         <v>714</v>
       </c>
-      <c r="D153" t="n">
-        <v>27</v>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -9677,8 +10963,12 @@
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
+      <c r="J153" t="n">
+        <v>0.4486</v>
+      </c>
+      <c r="K153" t="n">
+        <v>-30.17</v>
+      </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
@@ -9687,12 +10977,20 @@
         <v>2006</v>
       </c>
       <c r="Q153" t="inlineStr"/>
-      <c r="R153" t="inlineStr"/>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>p27-714</t>
+        </is>
+      </c>
       <c r="S153" t="inlineStr"/>
-      <c r="T153" t="inlineStr">
+      <c r="T153" t="inlineStr"/>
+      <c r="U153" t="inlineStr">
         <is>
           <t>Myrsine coriaceae</t>
         </is>
+      </c>
+      <c r="V153" t="n">
+        <v>0.4486</v>
       </c>
     </row>
   </sheetData>
